--- a/artfynd/A 38540-2024 artfynd.xlsx
+++ b/artfynd/A 38540-2024 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232872</v>
+        <v>121232874</v>
       </c>
       <c r="B8" t="n">
-        <v>88018</v>
+        <v>90715</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576820</v>
+        <v>576795</v>
       </c>
       <c r="R8" t="n">
-        <v>7187960</v>
+        <v>7187914</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232874</v>
+        <v>121232866</v>
       </c>
       <c r="B9" t="n">
-        <v>90705</v>
+        <v>94496</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,25 +1472,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2813</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576795</v>
+        <v>576880</v>
       </c>
       <c r="R9" t="n">
-        <v>7187914</v>
+        <v>7188090</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232870</v>
+        <v>121232831</v>
       </c>
       <c r="B10" t="n">
-        <v>82382</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,34 +1578,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576840</v>
+        <v>576882</v>
       </c>
       <c r="R10" t="n">
-        <v>7188066</v>
+        <v>7187886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232829</v>
+        <v>121232868</v>
       </c>
       <c r="B11" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576815</v>
+        <v>576879</v>
       </c>
       <c r="R11" t="n">
-        <v>7187932</v>
+        <v>7188076</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232876</v>
+        <v>121232870</v>
       </c>
       <c r="B12" t="n">
-        <v>91127</v>
+        <v>82385</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,25 +1788,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1811,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576841</v>
+        <v>576840</v>
       </c>
       <c r="R12" t="n">
-        <v>7188067</v>
+        <v>7188066</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232825</v>
+        <v>121232876</v>
       </c>
       <c r="B13" t="n">
-        <v>57348</v>
+        <v>91137</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,43 +1890,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576844</v>
+        <v>576841</v>
       </c>
       <c r="R13" t="n">
-        <v>7188074</v>
+        <v>7188067</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232831</v>
+        <v>121232834</v>
       </c>
       <c r="B14" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576882</v>
+        <v>576888</v>
       </c>
       <c r="R14" t="n">
-        <v>7187886</v>
+        <v>7187894</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,10 +2087,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232834</v>
+        <v>121232872</v>
       </c>
       <c r="B15" t="n">
-        <v>57348</v>
+        <v>88024</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,39 +2103,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576888</v>
+        <v>576820</v>
       </c>
       <c r="R15" t="n">
-        <v>7187894</v>
+        <v>7187960</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2194,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232868</v>
+        <v>121232829</v>
       </c>
       <c r="B16" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2239,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576879</v>
+        <v>576815</v>
       </c>
       <c r="R16" t="n">
-        <v>7188076</v>
+        <v>7187932</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232866</v>
+        <v>121232825</v>
       </c>
       <c r="B17" t="n">
-        <v>94486</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,38 +2308,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2813</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576880</v>
+        <v>576844</v>
       </c>
       <c r="R17" t="n">
-        <v>7188090</v>
+        <v>7188074</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 38540-2024 artfynd.xlsx
+++ b/artfynd/A 38540-2024 artfynd.xlsx
@@ -1460,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232866</v>
+        <v>121232831</v>
       </c>
       <c r="B9" t="n">
-        <v>94496</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,38 +1472,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2813</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576880</v>
+        <v>576882</v>
       </c>
       <c r="R9" t="n">
-        <v>7188090</v>
+        <v>7187886</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232831</v>
+        <v>121232866</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>94496</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,43 +1579,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2813</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576882</v>
+        <v>576880</v>
       </c>
       <c r="R10" t="n">
-        <v>7187886</v>
+        <v>7188090</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 38540-2024 artfynd.xlsx
+++ b/artfynd/A 38540-2024 artfynd.xlsx
@@ -1460,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232831</v>
+        <v>121232866</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>94496</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,43 +1472,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2813</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576882</v>
+        <v>576880</v>
       </c>
       <c r="R9" t="n">
-        <v>7187886</v>
+        <v>7188090</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232866</v>
+        <v>121232831</v>
       </c>
       <c r="B10" t="n">
-        <v>94496</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,38 +1574,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2813</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576880</v>
+        <v>576882</v>
       </c>
       <c r="R10" t="n">
-        <v>7188090</v>
+        <v>7187886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 38540-2024 artfynd.xlsx
+++ b/artfynd/A 38540-2024 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232874</v>
+        <v>121232872</v>
       </c>
       <c r="B8" t="n">
-        <v>90715</v>
+        <v>88024</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576795</v>
+        <v>576820</v>
       </c>
       <c r="R8" t="n">
-        <v>7187914</v>
+        <v>7187960</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232866</v>
+        <v>121232825</v>
       </c>
       <c r="B9" t="n">
-        <v>94496</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,38 +1472,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2813</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576880</v>
+        <v>576844</v>
       </c>
       <c r="R9" t="n">
-        <v>7188090</v>
+        <v>7188074</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1567,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232831</v>
+        <v>121232834</v>
       </c>
       <c r="B10" t="n">
         <v>57351</v>
@@ -1607,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576882</v>
+        <v>576888</v>
       </c>
       <c r="R10" t="n">
-        <v>7187886</v>
+        <v>7187894</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232868</v>
+        <v>121232829</v>
       </c>
       <c r="B11" t="n">
         <v>57351</v>
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576879</v>
+        <v>576815</v>
       </c>
       <c r="R11" t="n">
-        <v>7188076</v>
+        <v>7187932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1878,10 +1883,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232876</v>
+        <v>121232874</v>
       </c>
       <c r="B13" t="n">
-        <v>91137</v>
+        <v>90715</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1890,25 +1895,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1918,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576841</v>
+        <v>576795</v>
       </c>
       <c r="R13" t="n">
-        <v>7188067</v>
+        <v>7187914</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,10 +1985,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232834</v>
+        <v>121232876</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>91137</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,43 +1997,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576888</v>
+        <v>576841</v>
       </c>
       <c r="R14" t="n">
-        <v>7187894</v>
+        <v>7188067</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,10 +2087,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232872</v>
+        <v>121232866</v>
       </c>
       <c r="B15" t="n">
-        <v>88024</v>
+        <v>94496</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2099,25 +2099,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>2813</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576820</v>
+        <v>576880</v>
       </c>
       <c r="R15" t="n">
-        <v>7187960</v>
+        <v>7188090</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232829</v>
+        <v>121232868</v>
       </c>
       <c r="B16" t="n">
         <v>57351</v>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576815</v>
+        <v>576879</v>
       </c>
       <c r="R16" t="n">
-        <v>7187932</v>
+        <v>7188076</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,7 +2296,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232825</v>
+        <v>121232831</v>
       </c>
       <c r="B17" t="n">
         <v>57351</v>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576844</v>
+        <v>576882</v>
       </c>
       <c r="R17" t="n">
-        <v>7188074</v>
+        <v>7187886</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 38540-2024 artfynd.xlsx
+++ b/artfynd/A 38540-2024 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232872</v>
+        <v>121232874</v>
       </c>
       <c r="B8" t="n">
-        <v>88024</v>
+        <v>90727</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576820</v>
+        <v>576795</v>
       </c>
       <c r="R8" t="n">
-        <v>7187960</v>
+        <v>7187914</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232825</v>
+        <v>121232829</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576844</v>
+        <v>576815</v>
       </c>
       <c r="R9" t="n">
-        <v>7188074</v>
+        <v>7187932</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232834</v>
+        <v>121232866</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>94508</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,43 +1579,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2813</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576888</v>
+        <v>576880</v>
       </c>
       <c r="R10" t="n">
-        <v>7187894</v>
+        <v>7188090</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232829</v>
+        <v>121232872</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>88031</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,39 +1685,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576815</v>
+        <v>576820</v>
       </c>
       <c r="R11" t="n">
-        <v>7187932</v>
+        <v>7187960</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232870</v>
+        <v>121232825</v>
       </c>
       <c r="B12" t="n">
-        <v>82385</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,34 +1787,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576840</v>
+        <v>576844</v>
       </c>
       <c r="R12" t="n">
-        <v>7188066</v>
+        <v>7188074</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232874</v>
+        <v>121232834</v>
       </c>
       <c r="B13" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,34 +1894,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576795</v>
+        <v>576888</v>
       </c>
       <c r="R13" t="n">
-        <v>7187914</v>
+        <v>7187894</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1985,10 +1985,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232876</v>
+        <v>121232870</v>
       </c>
       <c r="B14" t="n">
-        <v>91137</v>
+        <v>82388</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1997,25 +1997,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576841</v>
+        <v>576840</v>
       </c>
       <c r="R14" t="n">
-        <v>7188067</v>
+        <v>7188066</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,10 +2087,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232866</v>
+        <v>121232831</v>
       </c>
       <c r="B15" t="n">
-        <v>94496</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2099,38 +2099,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2813</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576880</v>
+        <v>576882</v>
       </c>
       <c r="R15" t="n">
-        <v>7188090</v>
+        <v>7187886</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2296,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232831</v>
+        <v>121232876</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>91149</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2308,43 +2313,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576882</v>
+        <v>576841</v>
       </c>
       <c r="R17" t="n">
-        <v>7187886</v>
+        <v>7188067</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 38540-2024 artfynd.xlsx
+++ b/artfynd/A 38540-2024 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232874</v>
+        <v>121232876</v>
       </c>
       <c r="B8" t="n">
-        <v>90727</v>
+        <v>91150</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,25 +1370,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576795</v>
+        <v>576841</v>
       </c>
       <c r="R8" t="n">
-        <v>7187914</v>
+        <v>7188067</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232829</v>
+        <v>121232868</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576815</v>
+        <v>576879</v>
       </c>
       <c r="R9" t="n">
-        <v>7187932</v>
+        <v>7188076</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232866</v>
+        <v>121232874</v>
       </c>
       <c r="B10" t="n">
-        <v>94508</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,25 +1579,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2813</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576880</v>
+        <v>576795</v>
       </c>
       <c r="R10" t="n">
-        <v>7188090</v>
+        <v>7187914</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232872</v>
+        <v>121232825</v>
       </c>
       <c r="B11" t="n">
-        <v>88031</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,34 +1685,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576820</v>
+        <v>576844</v>
       </c>
       <c r="R11" t="n">
-        <v>7187960</v>
+        <v>7188074</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232825</v>
+        <v>121232872</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>88031</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,39 +1792,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576844</v>
+        <v>576820</v>
       </c>
       <c r="R12" t="n">
-        <v>7188074</v>
+        <v>7187960</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232834</v>
+        <v>121232870</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>82388</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,39 +1894,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576888</v>
+        <v>576840</v>
       </c>
       <c r="R13" t="n">
-        <v>7187894</v>
+        <v>7188066</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1985,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232870</v>
+        <v>121232831</v>
       </c>
       <c r="B14" t="n">
-        <v>82388</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2001,34 +1996,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576840</v>
+        <v>576882</v>
       </c>
       <c r="R14" t="n">
-        <v>7188066</v>
+        <v>7187886</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,7 +2087,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232831</v>
+        <v>121232829</v>
       </c>
       <c r="B15" t="n">
         <v>57351</v>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576882</v>
+        <v>576815</v>
       </c>
       <c r="R15" t="n">
-        <v>7187886</v>
+        <v>7187932</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232868</v>
+        <v>121232866</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>94509</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2206,43 +2206,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2813</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576879</v>
+        <v>576880</v>
       </c>
       <c r="R16" t="n">
-        <v>7188076</v>
+        <v>7188090</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232876</v>
+        <v>121232834</v>
       </c>
       <c r="B17" t="n">
-        <v>91149</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,38 +2308,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576841</v>
+        <v>576888</v>
       </c>
       <c r="R17" t="n">
-        <v>7188067</v>
+        <v>7187894</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 38540-2024 artfynd.xlsx
+++ b/artfynd/A 38540-2024 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232876</v>
+        <v>121232831</v>
       </c>
       <c r="B8" t="n">
-        <v>91150</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,38 +1370,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576841</v>
+        <v>576882</v>
       </c>
       <c r="R8" t="n">
-        <v>7188067</v>
+        <v>7187886</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232868</v>
+        <v>121232866</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>94512</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,43 +1477,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2813</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576879</v>
+        <v>576880</v>
       </c>
       <c r="R9" t="n">
-        <v>7188076</v>
+        <v>7188090</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232874</v>
+        <v>121232868</v>
       </c>
       <c r="B10" t="n">
-        <v>90728</v>
+        <v>57354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,34 +1583,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576795</v>
+        <v>576879</v>
       </c>
       <c r="R10" t="n">
-        <v>7187914</v>
+        <v>7188076</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1677,7 @@
         <v>121232825</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1776,10 +1781,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232872</v>
+        <v>121232834</v>
       </c>
       <c r="B12" t="n">
-        <v>88031</v>
+        <v>57354</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,34 +1797,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576820</v>
+        <v>576888</v>
       </c>
       <c r="R12" t="n">
-        <v>7187960</v>
+        <v>7187894</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1881,7 +1891,7 @@
         <v>121232870</v>
       </c>
       <c r="B13" t="n">
-        <v>82388</v>
+        <v>82391</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1980,10 +1990,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232831</v>
+        <v>121232872</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>88034</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1996,39 +2006,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576882</v>
+        <v>576820</v>
       </c>
       <c r="R14" t="n">
-        <v>7187886</v>
+        <v>7187960</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232829</v>
+        <v>121232876</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>91153</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2099,43 +2104,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576815</v>
+        <v>576841</v>
       </c>
       <c r="R15" t="n">
-        <v>7187932</v>
+        <v>7188067</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232866</v>
+        <v>121232829</v>
       </c>
       <c r="B16" t="n">
-        <v>94509</v>
+        <v>57354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2206,38 +2206,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2813</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576880</v>
+        <v>576815</v>
       </c>
       <c r="R16" t="n">
-        <v>7188090</v>
+        <v>7187932</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232834</v>
+        <v>121232874</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>90731</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,39 +2317,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576888</v>
+        <v>576795</v>
       </c>
       <c r="R17" t="n">
-        <v>7187894</v>
+        <v>7187914</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 38540-2024 artfynd.xlsx
+++ b/artfynd/A 38540-2024 artfynd.xlsx
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232866</v>
+        <v>121232876</v>
       </c>
       <c r="B9" t="n">
-        <v>94512</v>
+        <v>91153</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,25 +1477,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2813</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576880</v>
+        <v>576841</v>
       </c>
       <c r="R9" t="n">
-        <v>7188090</v>
+        <v>7188067</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232868</v>
+        <v>121232872</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>88034</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,39 +1583,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576879</v>
+        <v>576820</v>
       </c>
       <c r="R10" t="n">
-        <v>7188076</v>
+        <v>7187960</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232825</v>
+        <v>121232829</v>
       </c>
       <c r="B11" t="n">
         <v>57354</v>
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576844</v>
+        <v>576815</v>
       </c>
       <c r="R11" t="n">
-        <v>7188074</v>
+        <v>7187932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232834</v>
+        <v>121232874</v>
       </c>
       <c r="B12" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,39 +1792,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576888</v>
+        <v>576795</v>
       </c>
       <c r="R12" t="n">
-        <v>7187894</v>
+        <v>7187914</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1990,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232872</v>
+        <v>121232825</v>
       </c>
       <c r="B14" t="n">
-        <v>88034</v>
+        <v>57354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,34 +1996,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576820</v>
+        <v>576844</v>
       </c>
       <c r="R14" t="n">
-        <v>7187960</v>
+        <v>7188074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,10 +2087,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232876</v>
+        <v>121232866</v>
       </c>
       <c r="B15" t="n">
-        <v>91153</v>
+        <v>94512</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2104,25 +2099,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>2813</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2132,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576841</v>
+        <v>576880</v>
       </c>
       <c r="R15" t="n">
-        <v>7188067</v>
+        <v>7188090</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2194,7 +2189,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232829</v>
+        <v>121232834</v>
       </c>
       <c r="B16" t="n">
         <v>57354</v>
@@ -2239,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576815</v>
+        <v>576888</v>
       </c>
       <c r="R16" t="n">
-        <v>7187932</v>
+        <v>7187894</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232874</v>
+        <v>121232868</v>
       </c>
       <c r="B17" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,34 +2312,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576795</v>
+        <v>576879</v>
       </c>
       <c r="R17" t="n">
-        <v>7187914</v>
+        <v>7188076</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 38540-2024 artfynd.xlsx
+++ b/artfynd/A 38540-2024 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232831</v>
+        <v>121232870</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>82392</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,39 +1374,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576882</v>
+        <v>576840</v>
       </c>
       <c r="R8" t="n">
-        <v>7187886</v>
+        <v>7188066</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232876</v>
+        <v>121232874</v>
       </c>
       <c r="B9" t="n">
-        <v>91153</v>
+        <v>90737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,25 +1472,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1505,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576841</v>
+        <v>576795</v>
       </c>
       <c r="R9" t="n">
-        <v>7188067</v>
+        <v>7187914</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232872</v>
+        <v>121232866</v>
       </c>
       <c r="B10" t="n">
-        <v>88034</v>
+        <v>94518</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,25 +1574,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>2813</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1607,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576820</v>
+        <v>576880</v>
       </c>
       <c r="R10" t="n">
-        <v>7187960</v>
+        <v>7188090</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232829</v>
+        <v>121232876</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>91159</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,43 +1676,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576815</v>
+        <v>576841</v>
       </c>
       <c r="R11" t="n">
-        <v>7187932</v>
+        <v>7188067</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232874</v>
+        <v>121232834</v>
       </c>
       <c r="B12" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,34 +1782,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576795</v>
+        <v>576888</v>
       </c>
       <c r="R12" t="n">
-        <v>7187914</v>
+        <v>7187894</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232870</v>
+        <v>121232825</v>
       </c>
       <c r="B13" t="n">
-        <v>82391</v>
+        <v>57355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,34 +1889,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576840</v>
+        <v>576844</v>
       </c>
       <c r="R13" t="n">
-        <v>7188066</v>
+        <v>7188074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232825</v>
+        <v>121232831</v>
       </c>
       <c r="B14" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576844</v>
+        <v>576882</v>
       </c>
       <c r="R14" t="n">
-        <v>7188074</v>
+        <v>7187886</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,10 +2087,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232866</v>
+        <v>121232829</v>
       </c>
       <c r="B15" t="n">
-        <v>94512</v>
+        <v>57355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2099,38 +2099,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2813</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576880</v>
+        <v>576815</v>
       </c>
       <c r="R15" t="n">
-        <v>7188090</v>
+        <v>7187932</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,10 +2194,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232834</v>
+        <v>121232872</v>
       </c>
       <c r="B16" t="n">
-        <v>57354</v>
+        <v>88038</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,39 +2210,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576888</v>
+        <v>576820</v>
       </c>
       <c r="R16" t="n">
-        <v>7187894</v>
+        <v>7187960</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2299,7 +2299,7 @@
         <v>121232868</v>
       </c>
       <c r="B17" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 38540-2024 artfynd.xlsx
+++ b/artfynd/A 38540-2024 artfynd.xlsx
@@ -2194,10 +2194,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232872</v>
+        <v>121232868</v>
       </c>
       <c r="B16" t="n">
-        <v>88038</v>
+        <v>57355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,34 +2210,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576820</v>
+        <v>576879</v>
       </c>
       <c r="R16" t="n">
-        <v>7187960</v>
+        <v>7188076</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232868</v>
+        <v>121232872</v>
       </c>
       <c r="B17" t="n">
-        <v>57355</v>
+        <v>88038</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,39 +2317,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576879</v>
+        <v>576820</v>
       </c>
       <c r="R17" t="n">
-        <v>7188076</v>
+        <v>7187960</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 38540-2024 artfynd.xlsx
+++ b/artfynd/A 38540-2024 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232870</v>
+        <v>121232868</v>
       </c>
       <c r="B8" t="n">
-        <v>82392</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,34 +1374,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576840</v>
+        <v>576879</v>
       </c>
       <c r="R8" t="n">
-        <v>7188066</v>
+        <v>7188076</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232874</v>
+        <v>121232876</v>
       </c>
       <c r="B9" t="n">
-        <v>90737</v>
+        <v>91160</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,25 +1477,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576795</v>
+        <v>576841</v>
       </c>
       <c r="R9" t="n">
-        <v>7187914</v>
+        <v>7188067</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232866</v>
+        <v>121232829</v>
       </c>
       <c r="B10" t="n">
-        <v>94518</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,38 +1579,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2813</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576880</v>
+        <v>576815</v>
       </c>
       <c r="R10" t="n">
-        <v>7188090</v>
+        <v>7187932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232876</v>
+        <v>121232872</v>
       </c>
       <c r="B11" t="n">
-        <v>91159</v>
+        <v>88039</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,25 +1686,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1704,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576841</v>
+        <v>576820</v>
       </c>
       <c r="R11" t="n">
-        <v>7188067</v>
+        <v>7187960</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232834</v>
+        <v>121232874</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,39 +1792,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576888</v>
+        <v>576795</v>
       </c>
       <c r="R12" t="n">
-        <v>7187894</v>
+        <v>7187914</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232825</v>
+        <v>121232866</v>
       </c>
       <c r="B13" t="n">
-        <v>57355</v>
+        <v>94519</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,43 +1890,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2813</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576844</v>
+        <v>576880</v>
       </c>
       <c r="R13" t="n">
-        <v>7188074</v>
+        <v>7188090</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232831</v>
+        <v>121232825</v>
       </c>
       <c r="B14" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576882</v>
+        <v>576844</v>
       </c>
       <c r="R14" t="n">
-        <v>7187886</v>
+        <v>7188074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,10 +2087,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232829</v>
+        <v>121232870</v>
       </c>
       <c r="B15" t="n">
-        <v>57355</v>
+        <v>82393</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,39 +2103,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576815</v>
+        <v>576840</v>
       </c>
       <c r="R15" t="n">
-        <v>7187932</v>
+        <v>7188066</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2194,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232868</v>
+        <v>121232831</v>
       </c>
       <c r="B16" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2239,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576879</v>
+        <v>576882</v>
       </c>
       <c r="R16" t="n">
-        <v>7188076</v>
+        <v>7187886</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232872</v>
+        <v>121232834</v>
       </c>
       <c r="B17" t="n">
-        <v>88038</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,34 +2312,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576820</v>
+        <v>576888</v>
       </c>
       <c r="R17" t="n">
-        <v>7187960</v>
+        <v>7187894</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 38540-2024 artfynd.xlsx
+++ b/artfynd/A 38540-2024 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232868</v>
+        <v>121232874</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,39 +1374,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576879</v>
+        <v>576795</v>
       </c>
       <c r="R8" t="n">
-        <v>7188076</v>
+        <v>7187914</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232876</v>
+        <v>121232831</v>
       </c>
       <c r="B9" t="n">
-        <v>91160</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,38 +1472,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576841</v>
+        <v>576882</v>
       </c>
       <c r="R9" t="n">
-        <v>7188067</v>
+        <v>7187886</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232829</v>
+        <v>121232876</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>91160</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,43 +1579,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576815</v>
+        <v>576841</v>
       </c>
       <c r="R10" t="n">
-        <v>7187932</v>
+        <v>7188067</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232872</v>
+        <v>121232868</v>
       </c>
       <c r="B11" t="n">
-        <v>88039</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,34 +1685,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576820</v>
+        <v>576879</v>
       </c>
       <c r="R11" t="n">
-        <v>7187960</v>
+        <v>7188076</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232874</v>
+        <v>121232870</v>
       </c>
       <c r="B12" t="n">
-        <v>90738</v>
+        <v>82393</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576795</v>
+        <v>576840</v>
       </c>
       <c r="R12" t="n">
-        <v>7187914</v>
+        <v>7188066</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232866</v>
+        <v>121232834</v>
       </c>
       <c r="B13" t="n">
-        <v>94519</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1890,38 +1890,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2813</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576880</v>
+        <v>576888</v>
       </c>
       <c r="R13" t="n">
-        <v>7188090</v>
+        <v>7187894</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,10 +1985,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232825</v>
+        <v>121232866</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>94519</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,43 +1997,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2813</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576844</v>
+        <v>576880</v>
       </c>
       <c r="R14" t="n">
-        <v>7188074</v>
+        <v>7188090</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,10 +2087,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232870</v>
+        <v>121232825</v>
       </c>
       <c r="B15" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,34 +2103,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576840</v>
+        <v>576844</v>
       </c>
       <c r="R15" t="n">
-        <v>7188066</v>
+        <v>7188074</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,10 +2194,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232831</v>
+        <v>121232872</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>88039</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,39 +2210,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576882</v>
+        <v>576820</v>
       </c>
       <c r="R16" t="n">
-        <v>7187886</v>
+        <v>7187960</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,7 +2296,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232834</v>
+        <v>121232829</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576888</v>
+        <v>576815</v>
       </c>
       <c r="R17" t="n">
-        <v>7187894</v>
+        <v>7187932</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 38540-2024 artfynd.xlsx
+++ b/artfynd/A 38540-2024 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232874</v>
+        <v>121232831</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,34 +1374,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576795</v>
+        <v>576882</v>
       </c>
       <c r="R8" t="n">
-        <v>7187914</v>
+        <v>7187886</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1465,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232831</v>
+        <v>121232829</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1505,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576882</v>
+        <v>576815</v>
       </c>
       <c r="R9" t="n">
-        <v>7187886</v>
+        <v>7187932</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232876</v>
+        <v>121232834</v>
       </c>
       <c r="B10" t="n">
-        <v>91160</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,38 +1584,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576841</v>
+        <v>576888</v>
       </c>
       <c r="R10" t="n">
-        <v>7188067</v>
+        <v>7187894</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232868</v>
+        <v>121232876</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>91160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,43 +1691,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576879</v>
+        <v>576841</v>
       </c>
       <c r="R11" t="n">
-        <v>7188076</v>
+        <v>7188067</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,10 +1781,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232870</v>
+        <v>121232874</v>
       </c>
       <c r="B12" t="n">
-        <v>82393</v>
+        <v>90738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,21 +1797,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1816,10 +1821,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576840</v>
+        <v>576795</v>
       </c>
       <c r="R12" t="n">
-        <v>7188066</v>
+        <v>7187914</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,7 +1883,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232834</v>
+        <v>121232825</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1923,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576888</v>
+        <v>576844</v>
       </c>
       <c r="R13" t="n">
-        <v>7187894</v>
+        <v>7188074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1985,10 +1990,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232866</v>
+        <v>121232872</v>
       </c>
       <c r="B14" t="n">
-        <v>94519</v>
+        <v>88039</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1997,25 +2002,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2813</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2025,10 +2030,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576880</v>
+        <v>576820</v>
       </c>
       <c r="R14" t="n">
-        <v>7188090</v>
+        <v>7187960</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232825</v>
+        <v>121232866</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>94519</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2099,43 +2104,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2813</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576844</v>
+        <v>576880</v>
       </c>
       <c r="R15" t="n">
-        <v>7188074</v>
+        <v>7188090</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232872</v>
+        <v>121232868</v>
       </c>
       <c r="B16" t="n">
-        <v>88039</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,34 +2210,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576820</v>
+        <v>576879</v>
       </c>
       <c r="R16" t="n">
-        <v>7187960</v>
+        <v>7188076</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232829</v>
+        <v>121232870</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,39 +2317,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576815</v>
+        <v>576840</v>
       </c>
       <c r="R17" t="n">
-        <v>7187932</v>
+        <v>7188066</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 38540-2024 artfynd.xlsx
+++ b/artfynd/A 38540-2024 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232831</v>
+        <v>121232866</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>94519</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,43 +1370,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2813</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576882</v>
+        <v>576880</v>
       </c>
       <c r="R8" t="n">
-        <v>7187886</v>
+        <v>7188090</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232829</v>
+        <v>121232872</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>88039</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,39 +1476,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576815</v>
+        <v>576820</v>
       </c>
       <c r="R9" t="n">
-        <v>7187932</v>
+        <v>7187960</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232834</v>
+        <v>121232870</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,39 +1578,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576888</v>
+        <v>576840</v>
       </c>
       <c r="R10" t="n">
-        <v>7187894</v>
+        <v>7188066</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232876</v>
+        <v>121232825</v>
       </c>
       <c r="B11" t="n">
-        <v>91160</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,38 +1676,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576841</v>
+        <v>576844</v>
       </c>
       <c r="R11" t="n">
-        <v>7188067</v>
+        <v>7188074</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232874</v>
+        <v>121232868</v>
       </c>
       <c r="B12" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,34 +1787,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576795</v>
+        <v>576879</v>
       </c>
       <c r="R12" t="n">
-        <v>7187914</v>
+        <v>7188076</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1878,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232825</v>
+        <v>121232834</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1928,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576844</v>
+        <v>576888</v>
       </c>
       <c r="R13" t="n">
-        <v>7188074</v>
+        <v>7187894</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1990,10 +1985,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232872</v>
+        <v>121232831</v>
       </c>
       <c r="B14" t="n">
-        <v>88039</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,34 +2001,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576820</v>
+        <v>576882</v>
       </c>
       <c r="R14" t="n">
-        <v>7187960</v>
+        <v>7187886</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232866</v>
+        <v>121232829</v>
       </c>
       <c r="B15" t="n">
-        <v>94519</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2104,38 +2104,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2813</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576880</v>
+        <v>576815</v>
       </c>
       <c r="R15" t="n">
-        <v>7188090</v>
+        <v>7187932</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2194,10 +2199,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232868</v>
+        <v>121232876</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>91160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2206,43 +2211,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576879</v>
+        <v>576841</v>
       </c>
       <c r="R16" t="n">
-        <v>7188076</v>
+        <v>7188067</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232870</v>
+        <v>121232874</v>
       </c>
       <c r="B17" t="n">
-        <v>82393</v>
+        <v>90738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,21 +2317,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576840</v>
+        <v>576795</v>
       </c>
       <c r="R17" t="n">
-        <v>7188066</v>
+        <v>7187914</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 38540-2024 artfynd.xlsx
+++ b/artfynd/A 38540-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104002436</v>
+        <v>121232876</v>
       </c>
       <c r="B2" t="n">
-        <v>89832</v>
+        <v>91160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,20 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576841.4655084453</v>
+        <v>576841</v>
       </c>
       <c r="R2" t="n">
-        <v>7188067.023994779</v>
+        <v>7188067</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104002429</v>
+        <v>121232874</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,20 +811,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576795.423527834</v>
+        <v>576795</v>
       </c>
       <c r="R3" t="n">
-        <v>7187914.507486956</v>
+        <v>7187914</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104001940</v>
+        <v>121232872</v>
       </c>
       <c r="B4" t="n">
-        <v>85703</v>
+        <v>88039</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,24 +909,23 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576820.7055557629</v>
+        <v>576820</v>
       </c>
       <c r="R4" t="n">
-        <v>7187960.769360269</v>
+        <v>7187960</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104002479</v>
+        <v>121232870</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
+        <v>82393</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,20 +1015,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576840.2076636207</v>
+        <v>576840</v>
       </c>
       <c r="R5" t="n">
-        <v>7188066.139244516</v>
+        <v>7188066</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104002581</v>
+        <v>121232868</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,7 +1117,6 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -1169,17 +1124,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576879.209769726</v>
+        <v>576879</v>
       </c>
       <c r="R6" t="n">
-        <v>7188076.514990605</v>
+        <v>7188076</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,22 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104002744</v>
+        <v>121232866</v>
       </c>
       <c r="B7" t="n">
-        <v>93056</v>
+        <v>94519</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,20 +1224,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576880.9829286799</v>
+        <v>576880</v>
       </c>
       <c r="R7" t="n">
-        <v>7188090.628148215</v>
+        <v>7188090</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,22 +1260,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,22 +1280,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232866</v>
+        <v>121232825</v>
       </c>
       <c r="B8" t="n">
-        <v>94519</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,38 +1304,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2813</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576880</v>
+        <v>576844</v>
       </c>
       <c r="R8" t="n">
-        <v>7188090</v>
+        <v>7188074</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232872</v>
+        <v>121232834</v>
       </c>
       <c r="B9" t="n">
-        <v>88039</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,34 +1415,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576820</v>
+        <v>576888</v>
       </c>
       <c r="R9" t="n">
-        <v>7187960</v>
+        <v>7187894</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232870</v>
+        <v>121232831</v>
       </c>
       <c r="B10" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,34 +1522,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576840</v>
+        <v>576882</v>
       </c>
       <c r="R10" t="n">
-        <v>7188066</v>
+        <v>7187886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232825</v>
+        <v>121232829</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1709,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576844</v>
+        <v>576815</v>
       </c>
       <c r="R11" t="n">
-        <v>7188074</v>
+        <v>7187932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,638 +1717,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>121232868</v>
-      </c>
-      <c r="B12" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Björnberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>576879</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7188076</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>121232834</v>
-      </c>
-      <c r="B13" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Björnberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>576888</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7187894</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>121232831</v>
-      </c>
-      <c r="B14" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Björnberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>576882</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7187886</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>121232829</v>
-      </c>
-      <c r="B15" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Björnberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>576815</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7187932</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>121232876</v>
-      </c>
-      <c r="B16" t="n">
-        <v>91160</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Björnberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>576841</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7188067</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>121232874</v>
-      </c>
-      <c r="B17" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Björnberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>576795</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7187914</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38540-2024 artfynd.xlsx
+++ b/artfynd/A 38540-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121232876</v>
+        <v>121232872</v>
       </c>
       <c r="B2" t="n">
-        <v>91160</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576841</v>
+        <v>576820</v>
       </c>
       <c r="R2" t="n">
-        <v>7188067</v>
+        <v>7187960</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121232874</v>
+        <v>121232876</v>
       </c>
       <c r="B3" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576795</v>
+        <v>576841</v>
       </c>
       <c r="R3" t="n">
-        <v>7187914</v>
+        <v>7188067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121232872</v>
+        <v>121232870</v>
       </c>
       <c r="B4" t="n">
-        <v>88039</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576820</v>
+        <v>576840</v>
       </c>
       <c r="R4" t="n">
-        <v>7187960</v>
+        <v>7188066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121232870</v>
+        <v>121232866</v>
       </c>
       <c r="B5" t="n">
-        <v>82393</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>2813</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576840</v>
+        <v>576880</v>
       </c>
       <c r="R5" t="n">
-        <v>7188066</v>
+        <v>7188090</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121232868</v>
+        <v>121232823</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576879</v>
+        <v>576901</v>
       </c>
       <c r="R6" t="n">
-        <v>7188076</v>
+        <v>7188159</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,50 +1165,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121232866</v>
+        <v>121232825</v>
       </c>
       <c r="B7" t="n">
-        <v>94519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2813</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576880</v>
+        <v>576844</v>
       </c>
       <c r="R7" t="n">
-        <v>7188090</v>
+        <v>7188074</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,15 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232825</v>
+        <v>121232827</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,7 +1298,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1337,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576844</v>
+        <v>576785</v>
       </c>
       <c r="R8" t="n">
-        <v>7188074</v>
+        <v>7188013</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,15 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232834</v>
+        <v>121232829</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576888</v>
+        <v>576815</v>
       </c>
       <c r="R9" t="n">
-        <v>7187894</v>
+        <v>7187932</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,12 +1474,7 @@
         <v>121232831</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,15 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232829</v>
+        <v>121232834</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576815</v>
+        <v>576888</v>
       </c>
       <c r="R11" t="n">
-        <v>7187932</v>
+        <v>7187894</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,6 +1672,108 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121232868</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björnberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>576879</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7188076</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
